--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487192_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487192_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0854</v>
+        <v>4.1742</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1167</v>
+        <v>4.0354</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9687</v>
+        <v>0.1388</v>
       </c>
       <c r="G2" t="n">
         <v>3.0604</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1673</v>
+        <v>1.2562</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0462</v>
+        <v>-0.1276</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2136</v>
+        <v>1.3837</v>
       </c>
       <c r="V2" t="n">
         <v>0.2436</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4968</v>
+        <v>3.8171</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3936</v>
+        <v>3.5533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1032</v>
+        <v>0.2638</v>
       </c>
       <c r="G3" t="n">
         <v>2.5984</v>
@@ -688,13 +688,13 @@
         <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4719</v>
+        <v>-0.1517</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5949</v>
+        <v>-0.4352</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1229</v>
+        <v>0.2835</v>
       </c>
       <c r="V3" t="n">
         <v>0.9843</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0084</v>
+        <v>2.0352</v>
       </c>
       <c r="E4" t="n">
         <v>3.3056</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2972</v>
+        <v>-1.2704</v>
       </c>
       <c r="G4" t="n">
         <v>2.2764</v>
@@ -766,13 +766,13 @@
         <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4039</v>
+        <v>0.4306</v>
       </c>
       <c r="T4" t="n">
         <v>0.0132</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3906</v>
+        <v>0.4174</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2859</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7023</v>
+        <v>1.827</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1407</v>
+        <v>2.0253</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4384</v>
+        <v>-0.1983</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9642</v>
+        <v>-2.7002</v>
       </c>
       <c r="H5" t="n">
-        <v>0.439</v>
+        <v>1.0527</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5252</v>
+        <v>-3.7529</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3316</v>
+        <v>-0.5847</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1656</v>
+        <v>1.8008</v>
       </c>
       <c r="L5" t="n">
-        <v>3.166</v>
+        <v>-2.3855</v>
       </c>
       <c r="M5" t="n">
+        <v>-2.1155</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.7481</v>
+      </c>
+      <c r="O5" t="n">
         <v>-1.3674</v>
       </c>
-      <c r="N5" t="n">
-        <v>0.2734</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-1.6408</v>
-      </c>
       <c r="P5" t="n">
-        <v>-3.4741</v>
+        <v>1.3511</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.0532</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5983</v>
+        <v>0.4343</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3484</v>
+        <v>-0.1318</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2499</v>
+        <v>0.5661</v>
       </c>
       <c r="V5" t="n">
-        <v>0.614</v>
+        <v>2.7418</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5138</v>
+        <v>2.7418</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.772</v>
+        <v>0.927</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2648</v>
+        <v>1.4992</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4928</v>
+        <v>-0.5722</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.7002</v>
+        <v>1.9642</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0527</v>
+        <v>0.439</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.7529</v>
+        <v>1.5252</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5847</v>
+        <v>3.3316</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8008</v>
+        <v>0.1656</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.3855</v>
+        <v>3.166</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1155</v>
+        <v>-1.3674</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7481</v>
+        <v>0.2734</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3674</v>
+        <v>-1.6408</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3511</v>
+        <v>-3.4741</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.0532</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6207</v>
+        <v>1.823</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8923</v>
+        <v>0.7069</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2716</v>
+        <v>1.116</v>
       </c>
       <c r="V6" t="n">
-        <v>2.7418</v>
+        <v>0.614</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7418</v>
+        <v>1.5138</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0312</v>
+        <v>0.0491</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2713</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2401</v>
+        <v>0.3204</v>
       </c>
       <c r="G7" t="n">
         <v>0.1678</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0059</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>-0.119</v>
       </c>
       <c r="U7" t="n">
-        <v>0.113</v>
+        <v>0.1933</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7923</v>
+        <v>-0.5899</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0772</v>
+        <v>-0.1311</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.715</v>
+        <v>-0.4588</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4927</v>
+        <v>-1.0731</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4716</v>
+        <v>-0.002</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9789</v>
+        <v>-1.071</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8467</v>
+        <v>-0.1529</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3183</v>
+        <v>-0.3157</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5284</v>
+        <v>0.1628</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.354</v>
+        <v>-0.9202</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1533</v>
+        <v>0.3137</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5073</v>
+        <v>-1.2338</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.0881</v>
+        <v>0.193</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8454</v>
+        <v>0.2902</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5354</v>
+        <v>0.0218</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3808</v>
+        <v>0.2683</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4716</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1709</v>
+        <v>-0.6267</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3909</v>
+        <v>0.3828</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.78</v>
+        <v>-1.0095</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0731</v>
+        <v>1.4927</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.002</v>
+        <v>2.4716</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.071</v>
+        <v>-0.9789</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1529</v>
+        <v>2.8467</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3157</v>
+        <v>2.3183</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1628</v>
+        <v>0.5284</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9202</v>
+        <v>-1.354</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3137</v>
+        <v>0.1533</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2338</v>
+        <v>-1.5073</v>
       </c>
       <c r="P9" t="n">
-        <v>0.193</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R9" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2908</v>
+        <v>1.011</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.238</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0529</v>
+        <v>1.0863</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4716</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5101</v>
+        <v>-1.1721</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1309</v>
+        <v>0.8875</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3792</v>
+        <v>-2.0596</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5646</v>
+        <v>-0.6794</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0227</v>
+        <v>0.1574</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5873</v>
+        <v>-0.8368</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2634</v>
+        <v>1.4751</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0764</v>
+        <v>0.1242</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1871</v>
+        <v>1.3509</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.828</v>
+        <v>-2.1546</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0537</v>
+        <v>0.0332</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7743</v>
+        <v>-2.1878</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7021</v>
+        <v>0.772</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0881</v>
+        <v>-0.193</v>
       </c>
       <c r="R10" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>2.0425</v>
+        <v>-0.0367</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4079</v>
+        <v>-0.3946</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6345</v>
+        <v>0.3579</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5717</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7798</v>
+        <v>-2.2667</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6278</v>
+        <v>-1.1825</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4076</v>
+        <v>-1.0842</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6794</v>
+        <v>-2.2368</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1574</v>
+        <v>0.6728</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8368</v>
+        <v>-2.9096</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4751</v>
+        <v>-1.0758</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1242</v>
+        <v>0.7399</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3509</v>
+        <v>-1.8157</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1546</v>
+        <v>-1.161</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0332</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.1878</v>
+        <v>-1.0939</v>
       </c>
       <c r="P11" t="n">
+        <v>-2.1231</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-2.8951</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.772</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-0.193</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.965</v>
-      </c>
       <c r="S11" t="n">
-        <v>-0.6445</v>
+        <v>1.1511</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6544</v>
+        <v>0.3325</v>
       </c>
       <c r="U11" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.8186</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.228</v>
+        <v>0.9421</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.228</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6067</v>
+        <v>-2.4054</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4423</v>
+        <v>-0.9727</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1645</v>
+        <v>-1.4328</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2368</v>
+        <v>-0.5646</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6728</v>
+        <v>1.0227</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9096</v>
+        <v>-1.5873</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0758</v>
+        <v>1.2634</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7399</v>
+        <v>1.0764</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8157</v>
+        <v>0.1871</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.161</v>
+        <v>-1.828</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.0537</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0939</v>
+        <v>-1.7743</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1231</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8951</v>
+        <v>-3.0881</v>
       </c>
       <c r="R12" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8110000000000001</v>
+        <v>1.1471</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0727</v>
+        <v>0.5662</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7383</v>
+        <v>0.581</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9421</v>
+        <v>-0.2859</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4559</v>
+        <v>0.2859</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5138</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1739</v>
+        <v>5.768799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>12.5366</v>
+        <v>13.1315</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.3627</v>
+        <v>-7.362800000000001</v>
       </c>
       <c r="G13" t="n">
         <v>4.3058</v>
@@ -1438,7 +1438,7 @@
         <v>10.982</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.676100000000001</v>
+        <v>-6.6761</v>
       </c>
       <c r="J13" t="n">
         <v>20.8835</v>
@@ -1453,13 +1453,13 @@
         <v>-16.5778</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1694</v>
+        <v>-0.1693999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-16.4082</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.650300000000001</v>
+        <v>-9.6503</v>
       </c>
       <c r="Q13" t="n">
         <v>-18.3357</v>
@@ -1468,13 +1468,13 @@
         <v>8.6853</v>
       </c>
       <c r="S13" t="n">
-        <v>6.834600000000001</v>
+        <v>7.429500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2379999999999999</v>
+        <v>0.3571</v>
       </c>
       <c r="U13" t="n">
-        <v>7.0722</v>
+        <v>7.072099999999999</v>
       </c>
       <c r="V13" t="n">
         <v>3.683800000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.8726</v>
+        <v>10.4037</v>
       </c>
       <c r="E14" t="n">
-        <v>8.732799999999999</v>
+        <v>8.9331</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1398</v>
+        <v>1.4706</v>
       </c>
       <c r="G14" t="n">
         <v>7.8577</v>
@@ -1546,13 +1546,13 @@
         <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>0.15</v>
+        <v>-0.3189</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1752</v>
+        <v>-0.9749</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3252</v>
+        <v>0.656</v>
       </c>
       <c r="V14" t="n">
         <v>1.5138</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9334</v>
+        <v>4.9007</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9929</v>
+        <v>5.6924</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0594</v>
+        <v>-0.7917</v>
       </c>
       <c r="G15" t="n">
         <v>4.0673</v>
@@ -1624,13 +1624,13 @@
         <v>2.8951</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7588</v>
+        <v>-0.7915</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6266</v>
+        <v>-0.927</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1322</v>
+        <v>0.1355</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2702</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7345</v>
+        <v>-0.7881</v>
       </c>
       <c r="E16" t="n">
         <v>0.4308</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1654</v>
+        <v>-1.2189</v>
       </c>
       <c r="G16" t="n">
         <v>0.2589</v>
@@ -1702,13 +1702,13 @@
         <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0357</v>
+        <v>-0.0892</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2974</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2617</v>
+        <v>0.2082</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5717</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4542</v>
+        <v>-1.5207</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1739</v>
+        <v>1.9736</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.6281</v>
+        <v>-3.4942</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8952</v>
@@ -1780,13 +1780,13 @@
         <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3081</v>
+        <v>-1.3745</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8196</v>
+        <v>-1.0199</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4885</v>
+        <v>-0.3546</v>
       </c>
       <c r="V17" t="n">
         <v>1.5561</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4917</v>
+        <v>-2.1792</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2735</v>
+        <v>-3.194</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.7652</v>
+        <v>1.0148</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4499</v>
+        <v>-3.1963</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1347</v>
+        <v>-2.9964</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3152</v>
+        <v>-0.1999</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3793</v>
+        <v>-1.8487</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3143</v>
+        <v>-2.215</v>
       </c>
       <c r="L18" t="n">
-        <v>0.065</v>
+        <v>0.3663</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8292</v>
+        <v>-1.3476</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4489</v>
+        <v>-0.7813</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3802</v>
+        <v>-0.5662</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3511</v>
+        <v>2.3161</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3511</v>
+        <v>2.3161</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.265</v>
+        <v>-0.9287</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1057</v>
+        <v>-0.9749</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1593</v>
+        <v>0.0462</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1278</v>
+        <v>-0.3704</v>
       </c>
       <c r="W18" t="n">
+        <v>-0.3704</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-2.1278</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5937</v>
+        <v>-2.3855</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3943</v>
+        <v>0.4628</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8006</v>
+        <v>-2.8483</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.1963</v>
+        <v>0.2907</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9964</v>
+        <v>-1.388</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1999</v>
+        <v>1.6787</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8487</v>
+        <v>2.9659</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.215</v>
+        <v>-0.9005</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3663</v>
+        <v>3.8664</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3476</v>
+        <v>-2.6752</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7813</v>
+        <v>-0.4875</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5662</v>
+        <v>-2.1878</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3161</v>
+        <v>-0.579</v>
       </c>
       <c r="Q19" t="n">
+        <v>-1.9301</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3511</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.8692</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.5731000000000001</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.2961</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-1.228</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.3161</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-1.3431</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-1.1752</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.1679</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.3704</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-0.3704</v>
-      </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6929</v>
+        <v>-2.7653</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2625</v>
+        <v>0.9731</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9553</v>
+        <v>-3.7385</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2907</v>
+        <v>-1.4499</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.388</v>
+        <v>-0.1347</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6787</v>
+        <v>-1.3152</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9659</v>
+        <v>1.3793</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9005</v>
+        <v>1.3143</v>
       </c>
       <c r="L20" t="n">
-        <v>3.8664</v>
+        <v>0.065</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6752</v>
+        <v>-2.8292</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4875</v>
+        <v>-1.4489</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1878</v>
+        <v>-1.3802</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>1.3511</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1765</v>
+        <v>-0.5387</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7733</v>
+        <v>-0.4062</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4032</v>
+        <v>-0.1325</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.228</v>
+        <v>-2.1278</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.228</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0755</v>
+        <v>-5.3829</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.668</v>
+        <v>-3.8683</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4075</v>
+        <v>-1.5146</v>
       </c>
       <c r="G21" t="n">
         <v>-6.2044</v>
@@ -2092,13 +2092,13 @@
         <v>2.5091</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4574</v>
+        <v>-0.7648</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6266</v>
+        <v>-0.8269</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1692</v>
+        <v>0.0621</v>
       </c>
       <c r="V21" t="n">
         <v>0.0422</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9375</v>
+        <v>-5.4566</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4414</v>
+        <v>-4.0408</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.496</v>
+        <v>-1.4157</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0346</v>
@@ -2170,13 +2170,13 @@
         <v>2.8951</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6399</v>
+        <v>-1.159</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4726</v>
+        <v>-1.0721</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1673</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.173999999999999</v>
+        <v>-5.173899999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>7.362700000000002</v>
+        <v>7.362699999999998</v>
       </c>
       <c r="F23" t="n">
         <v>-12.5365</v>
@@ -2248,13 +2248,13 @@
         <v>18.3358</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.8345</v>
+        <v>-6.834499999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-7.0722</v>
+        <v>-7.072399999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2376999999999998</v>
+        <v>0.2379</v>
       </c>
       <c r="V23" t="n">
         <v>-3.684</v>
